--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,9 +790,122 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137123334</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Örsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>674385</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6633657</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Husby-Långhundra</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137123334</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137123334</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137123334</v>
       </c>
       <c r="B3" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137123334</v>
       </c>
       <c r="B3" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137123334</v>
       </c>
       <c r="B3" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137123334</v>
       </c>
       <c r="B3" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37356-2026 artfynd.xlsx
+++ b/artfynd/A 37356-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137093762</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137123334</v>
       </c>
       <c r="B3" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
